--- a/data/alopez.xlsx
+++ b/data/alopez.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/Resumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{9EF35FB9-12F6-40C8-8DFC-BB924313FB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0806E4D7-8F0E-4D72-98F7-3515B77D4A84}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{9EF35FB9-12F6-40C8-8DFC-BB924313FB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95F6AC66-CC56-4844-B311-FBF95F5F8E5B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7A27F12D-6F9D-4758-B7D5-03B08667753E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="16">
   <si>
     <t>Fecha</t>
   </si>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEB1E01-21BC-442C-965D-94DEC222FAE4}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1365,35 +1365,222 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" ref="D20" si="61">+D19+E19+K19-F19</f>
+        <f t="shared" ref="D20:D24" si="61">+D19+E19+K19-F19</f>
         <v>8267.6720000000023</v>
+      </c>
+      <c r="G20" s="2">
+        <v>115.75</v>
       </c>
       <c r="H20" s="4">
         <f t="shared" si="54"/>
-        <v>2576.9</v>
+        <v>2692.65</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>13.889999999999999</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="56"/>
-        <v>309.22800000000007</v>
+        <v>323.11800000000005</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>101.86</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="58"/>
-        <v>2267.672</v>
+        <v>2369.5320000000002</v>
       </c>
       <c r="M20" s="4">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>3.3953333333333333</v>
       </c>
       <c r="N20" s="5">
         <f t="shared" si="60"/>
+        <v>1.4000313510260201E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="3">
+        <f t="shared" si="61"/>
+        <v>8369.5320000000029</v>
+      </c>
+      <c r="G21" s="2">
+        <v>192.5</v>
+      </c>
+      <c r="H21" s="4">
+        <f t="shared" ref="H21:H24" si="62">+H20+G21</f>
+        <v>2885.15</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" ref="I21:I24" si="63">+G21*0.12</f>
+        <v>23.099999999999998</v>
+      </c>
+      <c r="J21" s="4">
+        <f t="shared" ref="J21:J24" si="64">+J20+I21</f>
+        <v>346.21800000000007</v>
+      </c>
+      <c r="K21" s="4">
+        <f t="shared" ref="K21:K24" si="65">+G21-I21</f>
+        <v>169.4</v>
+      </c>
+      <c r="L21" s="4">
+        <f t="shared" ref="L21:L24" si="66">+L20+K21</f>
+        <v>2538.9320000000002</v>
+      </c>
+      <c r="M21" s="4">
+        <f t="shared" ref="M21:M24" si="67">+K21/30</f>
+        <v>5.6466666666666665</v>
+      </c>
+      <c r="N21" s="5">
+        <f t="shared" ref="N21:N24" si="68">+G21/D21</f>
+        <v>2.3000091283479164E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>45932</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" si="61"/>
+        <v>8538.9320000000025</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G22" s="2">
+        <v>179.32</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="62"/>
+        <v>3064.4700000000003</v>
+      </c>
+      <c r="I22" s="4">
+        <f t="shared" si="63"/>
+        <v>21.5184</v>
+      </c>
+      <c r="J22" s="4">
+        <f t="shared" si="64"/>
+        <v>367.73640000000006</v>
+      </c>
+      <c r="K22" s="4">
+        <f t="shared" si="65"/>
+        <v>157.80160000000001</v>
+      </c>
+      <c r="L22" s="4">
+        <f t="shared" si="66"/>
+        <v>2696.7336000000005</v>
+      </c>
+      <c r="M22" s="4">
+        <f t="shared" si="67"/>
+        <v>5.2600533333333335</v>
+      </c>
+      <c r="N22" s="5">
+        <f t="shared" si="68"/>
+        <v>2.1000284344693216E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" si="61"/>
+        <v>10696.733600000003</v>
+      </c>
+      <c r="G23" s="2">
+        <v>385.08</v>
+      </c>
+      <c r="H23" s="4">
+        <f t="shared" si="62"/>
+        <v>3449.55</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="63"/>
+        <v>46.209599999999995</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="64"/>
+        <v>413.94600000000003</v>
+      </c>
+      <c r="K23" s="4">
+        <f t="shared" si="65"/>
+        <v>338.87040000000002</v>
+      </c>
+      <c r="L23" s="4">
+        <f t="shared" si="66"/>
+        <v>3035.6040000000003</v>
+      </c>
+      <c r="M23" s="4">
+        <f t="shared" si="67"/>
+        <v>11.295680000000001</v>
+      </c>
+      <c r="N23" s="5">
+        <f t="shared" si="68"/>
+        <v>3.5999774734971415E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>45993</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" si="61"/>
+        <v>11035.604000000003</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" si="62"/>
+        <v>3449.55</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <f t="shared" si="64"/>
+        <v>413.94600000000003</v>
+      </c>
+      <c r="K24" s="4">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="4">
+        <f t="shared" si="66"/>
+        <v>3035.6040000000003</v>
+      </c>
+      <c r="M24" s="4">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
     </row>

--- a/data/alopez.xlsx
+++ b/data/alopez.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0454BD8F-6B72-49F3-AE60-1BBDCDD9E496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{0454BD8F-6B72-49F3-AE60-1BBDCDD9E496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{550B62B0-7FDB-4D5A-9172-48C82F35FA3F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7A27F12D-6F9D-4758-B7D5-03B08667753E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="16">
   <si>
     <t>Fecha</t>
   </si>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEB1E01-21BC-442C-965D-94DEC222FAE4}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1693,33 +1693,174 @@
         <f t="shared" si="69"/>
         <v>11583.122400000004</v>
       </c>
+      <c r="G27" s="2">
+        <v>149.22999999999999</v>
+      </c>
       <c r="H27" s="4">
         <f t="shared" si="70"/>
-        <v>4071.73</v>
+        <v>4220.96</v>
       </c>
       <c r="I27" s="4">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>17.907599999999999</v>
       </c>
       <c r="J27" s="4">
         <f t="shared" si="72"/>
-        <v>488.60760000000005</v>
+        <v>506.51520000000005</v>
       </c>
       <c r="K27" s="4">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>131.32239999999999</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="74"/>
-        <v>3583.1224000000002</v>
+        <v>3714.4448000000002</v>
       </c>
       <c r="M27" s="4">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>4.3774133333333332</v>
       </c>
       <c r="N27" s="5">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>1.2883400075268128E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" ref="D28:D30" si="77">+D27+E27+K27-F27</f>
+        <v>11714.444800000003</v>
+      </c>
+      <c r="G28" s="2">
+        <v>79.010000000000005</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" ref="H28:H30" si="78">+H27+G28</f>
+        <v>4299.97</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" ref="I28:I30" si="79">+G28*0.12</f>
+        <v>9.4811999999999994</v>
+      </c>
+      <c r="J28" s="4">
+        <f t="shared" ref="J28:J30" si="80">+J27+I28</f>
+        <v>515.99639999999999</v>
+      </c>
+      <c r="K28" s="4">
+        <f t="shared" ref="K28:K30" si="81">+G28-I28</f>
+        <v>69.528800000000004</v>
+      </c>
+      <c r="L28" s="4">
+        <f t="shared" ref="L28:L30" si="82">+L27+K28</f>
+        <v>3783.9736000000003</v>
+      </c>
+      <c r="M28" s="4">
+        <f t="shared" ref="M28:M30" si="83">+K28/30</f>
+        <v>2.3176266666666669</v>
+      </c>
+      <c r="N28" s="5">
+        <f t="shared" ref="N28:N30" si="84">+G28/D28</f>
+        <v>6.7446645017269604E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="3">
+        <f t="shared" si="77"/>
+        <v>11783.973600000003</v>
+      </c>
+      <c r="G29" s="2">
+        <v>280.52</v>
+      </c>
+      <c r="H29" s="4">
+        <f t="shared" si="78"/>
+        <v>4580.49</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="79"/>
+        <v>33.662399999999998</v>
+      </c>
+      <c r="J29" s="4">
+        <f t="shared" si="80"/>
+        <v>549.65880000000004</v>
+      </c>
+      <c r="K29" s="4">
+        <f t="shared" si="81"/>
+        <v>246.85759999999999</v>
+      </c>
+      <c r="L29" s="4">
+        <f t="shared" si="82"/>
+        <v>4030.8312000000001</v>
+      </c>
+      <c r="M29" s="4">
+        <f t="shared" si="83"/>
+        <v>8.2285866666666667</v>
+      </c>
+      <c r="N29" s="5">
+        <f t="shared" si="84"/>
+        <v>2.3805212869791214E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="3">
+        <f t="shared" si="77"/>
+        <v>12030.831200000002</v>
+      </c>
+      <c r="G30" s="2">
+        <v>218.78</v>
+      </c>
+      <c r="H30" s="4">
+        <f t="shared" si="78"/>
+        <v>4799.2699999999995</v>
+      </c>
+      <c r="I30" s="4">
+        <f t="shared" si="79"/>
+        <v>26.253599999999999</v>
+      </c>
+      <c r="J30" s="4">
+        <f t="shared" si="80"/>
+        <v>575.91240000000005</v>
+      </c>
+      <c r="K30" s="4">
+        <f t="shared" si="81"/>
+        <v>192.5264</v>
+      </c>
+      <c r="L30" s="4">
+        <f t="shared" si="82"/>
+        <v>4223.3576000000003</v>
+      </c>
+      <c r="M30" s="4">
+        <f t="shared" si="83"/>
+        <v>6.4175466666666665</v>
+      </c>
+      <c r="N30" s="5">
+        <f t="shared" si="84"/>
+        <v>1.8184944694428093E-2</v>
       </c>
     </row>
   </sheetData>
